--- a/700 HK.xlsx
+++ b/700 HK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8BD0BB-2F9E-4195-9DB6-2DDCA806753D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EFF8C68-A775-4D45-8080-DCA99B34D999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38940" yWindow="2770" windowWidth="24340" windowHeight="15680" activeTab="1" xr2:uid="{C183CDF4-DAE3-4211-A459-AE4D0C2142B8}"/>
+    <workbookView xWindow="18910" yWindow="6660" windowWidth="19170" windowHeight="13220" xr2:uid="{C183CDF4-DAE3-4211-A459-AE4D0C2142B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>629</v>
+        <v>472.2</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="13" x14ac:dyDescent="0.3">
@@ -881,7 +881,7 @@
       </c>
       <c r="L4" s="3">
         <f>L2*L3</f>
-        <v>5722013</v>
+        <v>4295603.3999999994</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
@@ -921,7 +921,7 @@
       </c>
       <c r="L7" s="3">
         <f>L4-L5+L6</f>
-        <v>5647421</v>
+        <v>4221011.3999999994</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
